--- a/dataset_t6_grouped/results2/G1/G1_T6020_W0056F0003T0006Z000C1N27_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T6020_W0056F0003T0006Z000C1N27_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>9.286189177340185</v>
+        <v>1.50900574131778</v>
       </c>
       <c r="D2" t="n">
-        <v>15.72858136541389</v>
+        <v>2.555894471879757</v>
       </c>
       <c r="E2" t="n">
-        <v>18.87043622779419</v>
+        <v>3.066445887016556</v>
       </c>
       <c r="F2" t="n">
-        <v>18.8750444462779</v>
+        <v>3.067194722520159</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>37.58542871555126</v>
+        <v>6.10763216627708</v>
       </c>
       <c r="D3" t="n">
-        <v>12.95219719989109</v>
+        <v>2.104732044982303</v>
       </c>
       <c r="E3" t="n">
-        <v>18.87043622779419</v>
+        <v>3.066445887016556</v>
       </c>
       <c r="F3" t="n">
-        <v>18.8750444462779</v>
+        <v>3.067194722520159</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>12.09835449166107</v>
+        <v>1.965982604894924</v>
       </c>
       <c r="D4" t="n">
-        <v>21.00330661798015</v>
+        <v>3.413037325421775</v>
       </c>
       <c r="E4" t="n">
-        <v>18.87043622779419</v>
+        <v>3.066445887016556</v>
       </c>
       <c r="F4" t="n">
-        <v>18.8750444462779</v>
+        <v>3.067194722520159</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>24.88338136154561</v>
+        <v>4.043549471251161</v>
       </c>
       <c r="D5" t="n">
-        <v>22.33512697867087</v>
+        <v>3.629458134034017</v>
       </c>
       <c r="E5" t="n">
-        <v>18.87043622779419</v>
+        <v>3.066445887016556</v>
       </c>
       <c r="F5" t="n">
-        <v>18.8750444462779</v>
+        <v>3.067194722520159</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>60.86732382949872</v>
+        <v>9.890940122293541</v>
       </c>
       <c r="D6" t="n">
-        <v>64.41174991049553</v>
+        <v>10.46690936045552</v>
       </c>
       <c r="E6" t="n">
-        <v>18.87043622779419</v>
+        <v>3.066445887016556</v>
       </c>
       <c r="F6" t="n">
-        <v>18.8750444462779</v>
+        <v>3.067194722520159</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
